--- a/knowledge/Corpus_Source_Register.xlsx
+++ b/knowledge/Corpus_Source_Register.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Register" sheetId="1" r:id="R8276fb95b35c4bd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Register" sheetId="1" r:id="Rfae6cd8be9f641f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -29,7 +29,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -41,8 +41,13 @@
         <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF203864"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="2">
     <x:border>
       <x:left/>
       <x:right/>
@@ -50,11 +55,26 @@
       <x:bottom/>
       <x:diagonal/>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -70,11 +90,48 @@
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CorpusSources" displayName="CorpusSources" ref="A1:H20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="source_id"/>
+    <x:tableColumn id="2" name="source_name"/>
+    <x:tableColumn id="3" name="file_path"/>
+    <x:tableColumn id="4" name="source_type"/>
+    <x:tableColumn id="5" name="origin"/>
+    <x:tableColumn id="6" name="authority"/>
+    <x:tableColumn id="7" name="purpose"/>
+    <x:tableColumn id="8" name="access_status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -272,173 +329,540 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="50" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="65" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="35" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="70" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="12" t="str">
         <x:v>source_id</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="12" t="str">
         <x:v>source_name</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>file_path</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>source_type</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>origin</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>authority</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="12" t="str">
         <x:v>purpose</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="12" t="str">
         <x:v>access_status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="85" customHeight="1">
-      <x:c r="A2" s="4" t="str">
+    <x:row r="2" ht="60" customHeight="1">
+      <x:c r="A2" s="13" t="str">
         <x:v>SRC-001</x:v>
       </x:c>
-      <x:c r="B2" s="4" t="str">
+      <x:c r="B2" s="13" t="str">
         <x:v>Project Charter</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="str">
+      <x:c r="C2" s="13" t="str">
         <x:v>knowledge/corpus/project_charter.md</x:v>
       </x:c>
-      <x:c r="D2" s="4" t="str">
+      <x:c r="D2" s="13" t="str">
         <x:v>Project document</x:v>
       </x:c>
-      <x:c r="E2" s="4" t="str">
+      <x:c r="E2" s="13" t="str">
         <x:v>Project team</x:v>
       </x:c>
-      <x:c r="F2" s="4" t="str">
+      <x:c r="F2" s="13" t="str">
         <x:v>Primary</x:v>
       </x:c>
-      <x:c r="G2" s="4" t="str">
+      <x:c r="G2" s="13" t="str">
         <x:v>Defines the project problem target users objectives scope assumptions and constraints</x:v>
       </x:c>
-      <x:c r="H2" s="4" t="str">
-        <x:v>Authorized</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="85" customHeight="1">
-      <x:c r="A3" s="4" t="str">
+      <x:c r="H2" s="13" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="60" customHeight="1">
+      <x:c r="A3" s="13" t="str">
         <x:v>SRC-002</x:v>
       </x:c>
-      <x:c r="B3" s="4" t="str">
+      <x:c r="B3" s="13" t="str">
         <x:v>User Stories and Acceptance Criteria</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="str">
+      <x:c r="C3" s="13" t="str">
         <x:v>knowledge/corpus/user_stories.md</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str">
+      <x:c r="D3" s="13" t="str">
         <x:v>Requirements document</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
+      <x:c r="E3" s="13" t="str">
         <x:v>Project team</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
+      <x:c r="F3" s="13" t="str">
         <x:v>Primary</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="str">
+      <x:c r="G3" s="13" t="str">
         <x:v>Defines user stories requirements and acceptance criteria</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="str">
-        <x:v>Authorized</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="85" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="H3" s="13" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="60" customHeight="1">
+      <x:c r="A4" s="13" t="str">
         <x:v>SRC-003</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
+      <x:c r="B4" s="13" t="str">
         <x:v>AI Boundary Matrix</x:v>
       </x:c>
-      <x:c r="C4" s="4" t="str">
+      <x:c r="C4" s="13" t="str">
         <x:v>knowledge/corpus/ai_boundary_matrix.md</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="str">
+      <x:c r="D4" s="13" t="str">
         <x:v>Project control document</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="str">
+      <x:c r="E4" s="13" t="str">
         <x:v>Project team</x:v>
       </x:c>
-      <x:c r="F4" s="4" t="str">
+      <x:c r="F4" s="13" t="str">
         <x:v>Primary</x:v>
       </x:c>
-      <x:c r="G4" s="4" t="str">
+      <x:c r="G4" s="13" t="str">
         <x:v>Defines AI responsibilities deterministic responsibilities and human approval boundaries</x:v>
       </x:c>
-      <x:c r="H4" s="4" t="str">
-        <x:v>Authorized</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="85" customHeight="1">
-      <x:c r="A5" s="4" t="str">
+      <x:c r="H4" s="13" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="60" customHeight="1">
+      <x:c r="A5" s="13" t="str">
         <x:v>SRC-014</x:v>
       </x:c>
-      <x:c r="B5" s="4" t="str">
+      <x:c r="B5" s="13" t="str">
         <x:v>Tool Catalogue</x:v>
       </x:c>
-      <x:c r="C5" s="4" t="str">
+      <x:c r="C5" s="13" t="str">
         <x:v>knowledge/corpus/tool_catalogue.md</x:v>
       </x:c>
-      <x:c r="D5" s="4" t="str">
+      <x:c r="D5" s="13" t="str">
         <x:v>Architecture document</x:v>
       </x:c>
-      <x:c r="E5" s="4" t="str">
+      <x:c r="E5" s="13" t="str">
         <x:v>Project team</x:v>
       </x:c>
-      <x:c r="F5" s="4" t="str">
+      <x:c r="F5" s="13" t="str">
         <x:v>Primary</x:v>
       </x:c>
-      <x:c r="G5" s="4" t="str">
+      <x:c r="G5" s="13" t="str">
         <x:v>Defines Week 4 tool contracts schemas authorization and failure behaviour</x:v>
       </x:c>
-      <x:c r="H5" s="4" t="str">
-        <x:v>Authorized</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="85" customHeight="1">
-      <x:c r="A6" s="4" t="str">
+      <x:c r="H5" s="13" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
+      <x:c r="A6" s="13" t="str">
         <x:v>SRC-015</x:v>
       </x:c>
-      <x:c r="B6" s="4" t="str">
+      <x:c r="B6" s="13" t="str">
         <x:v>Agent Task Contract</x:v>
       </x:c>
-      <x:c r="C6" s="4" t="str">
+      <x:c r="C6" s="13" t="str">
         <x:v>knowledge/corpus/agent_task_contract.md</x:v>
       </x:c>
-      <x:c r="D6" s="4" t="str">
+      <x:c r="D6" s="13" t="str">
         <x:v>Architecture document</x:v>
       </x:c>
-      <x:c r="E6" s="4" t="str">
+      <x:c r="E6" s="13" t="str">
         <x:v>Project team</x:v>
       </x:c>
-      <x:c r="F6" s="4" t="str">
+      <x:c r="F6" s="13" t="str">
         <x:v>Primary</x:v>
       </x:c>
-      <x:c r="G6" s="4" t="str">
+      <x:c r="G6" s="13" t="str">
         <x:v>Defines the Week 5 bounded agent task goal tools state limits stop conditions and human hand-off</x:v>
       </x:c>
-      <x:c r="H6" s="4" t="str">
+      <x:c r="H6" s="13" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="110" customHeight="1">
+      <x:c r="A7" s="13" t="str">
+        <x:v>SRC-016</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="str">
+        <x:v>BudgetMe implementation and features</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>knowledge/corpus/budgetme_features.md</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="str">
+        <x:v>Source-derived repository document</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; upstream paths listed in document</x:v>
+      </x:c>
+      <x:c r="F7" s="13" t="str">
+        <x:v>Primary source code; derived summary</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="str">
+        <x:v>Describes inspected BudgetMe implementation; runtime and requirement approval unverified</x:v>
+      </x:c>
+      <x:c r="H7" s="13" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="110" customHeight="1">
+      <x:c r="A8" s="13" t="str">
+        <x:v>SRC-017</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="str">
+        <x:v>BudgetMe architecture</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="str">
+        <x:v>knowledge/corpus/budgetme_architecture.md</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="str">
+        <x:v>Source-derived repository document</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; upstream paths listed in document</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="str">
+        <x:v>Primary source code; derived summary</x:v>
+      </x:c>
+      <x:c r="G8" s="13" t="str">
+        <x:v>Describes inspected BudgetMe implementation; runtime and requirement approval unverified</x:v>
+      </x:c>
+      <x:c r="H8" s="13" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="110" customHeight="1">
+      <x:c r="A9" s="13" t="str">
+        <x:v>SRC-018</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="str">
+        <x:v>BudgetMe routes and API evidence</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>knowledge/corpus/budgetme_api.md</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="str">
+        <x:v>Source-derived repository document</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; upstream paths listed in document</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="str">
+        <x:v>Primary source code; derived summary</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="str">
+        <x:v>Describes inspected BudgetMe implementation; runtime and requirement approval unverified</x:v>
+      </x:c>
+      <x:c r="H9" s="13" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="110" customHeight="1">
+      <x:c r="A10" s="13" t="str">
+        <x:v>SRC-019</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="str">
+        <x:v>BudgetMe testing evidence and gaps</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="str">
+        <x:v>knowledge/corpus/budgetme_testing.md</x:v>
+      </x:c>
+      <x:c r="D10" s="13" t="str">
+        <x:v>Source-derived repository document</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; upstream paths listed in document</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="str">
+        <x:v>Primary source code; derived summary</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="str">
+        <x:v>Describes inspected BudgetMe implementation; runtime and requirement approval unverified</x:v>
+      </x:c>
+      <x:c r="H10" s="13" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A11" s="10" t="str">
+        <x:v>SRC-020</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>budgetme account access and budget ownership</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>knowledge/corpus/budgetme_requirements_001_005.md</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>Source-derived SRS extract</x:v>
+      </x:c>
+      <x:c r="E11" s="10" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; SRS=C:/Users/HP/Desktop/capstone/BudgetMe_Software_Requirements_Specification.docx; SRS_version=1.0; SRS_sha256=d90dd05f4a43bb17699eb6787672cc55571e65617c462fdcf08a26688eddad22</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="str">
+        <x:v>Source-derived requirements; PT targets distinguished</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="str">
+        <x:v>Preserves FR-001 to FR-005, their acceptance criteria, related quality targets and unresolved decisions.</x:v>
+      </x:c>
+      <x:c r="H11" s="10" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A12" s="10" t="str">
+        <x:v>SRC-021</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>budgetme planning categories and periods</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str">
+        <x:v>knowledge/corpus/budgetme_requirements_006_010.md</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="str">
+        <x:v>Source-derived SRS extract</x:v>
+      </x:c>
+      <x:c r="E12" s="10" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; SRS=C:/Users/HP/Desktop/capstone/BudgetMe_Software_Requirements_Specification.docx; SRS_version=1.0; SRS_sha256=d90dd05f4a43bb17699eb6787672cc55571e65617c462fdcf08a26688eddad22</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="str">
+        <x:v>Source-derived requirements; PT targets distinguished</x:v>
+      </x:c>
+      <x:c r="G12" s="10" t="str">
+        <x:v>Preserves FR-006 to FR-010, their acceptance criteria, related quality targets and unresolved decisions.</x:v>
+      </x:c>
+      <x:c r="H12" s="10" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A13" s="10" t="str">
+        <x:v>SRC-022</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>budgetme reporting balance and movement selection</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str">
+        <x:v>knowledge/corpus/budgetme_requirements_011_015.md</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="str">
+        <x:v>Source-derived SRS extract</x:v>
+      </x:c>
+      <x:c r="E13" s="10" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; SRS=C:/Users/HP/Desktop/capstone/BudgetMe_Software_Requirements_Specification.docx; SRS_version=1.0; SRS_sha256=d90dd05f4a43bb17699eb6787672cc55571e65617c462fdcf08a26688eddad22</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="str">
+        <x:v>Source-derived requirements; PT targets distinguished</x:v>
+      </x:c>
+      <x:c r="G13" s="10" t="str">
+        <x:v>Preserves FR-011 to FR-015, their acceptance criteria, related quality targets and unresolved decisions.</x:v>
+      </x:c>
+      <x:c r="H13" s="10" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A14" s="10" t="str">
+        <x:v>SRC-023</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>budgetme movement validation and manual savings</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str">
+        <x:v>knowledge/corpus/budgetme_requirements_016_020.md</x:v>
+      </x:c>
+      <x:c r="D14" s="10" t="str">
+        <x:v>Source-derived SRS extract</x:v>
+      </x:c>
+      <x:c r="E14" s="10" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; SRS=C:/Users/HP/Desktop/capstone/BudgetMe_Software_Requirements_Specification.docx; SRS_version=1.0; SRS_sha256=d90dd05f4a43bb17699eb6787672cc55571e65617c462fdcf08a26688eddad22</x:v>
+      </x:c>
+      <x:c r="F14" s="10" t="str">
+        <x:v>Source-derived requirements; PT targets distinguished</x:v>
+      </x:c>
+      <x:c r="G14" s="10" t="str">
+        <x:v>Preserves FR-016 to FR-020, their acceptance criteria, related quality targets and unresolved decisions.</x:v>
+      </x:c>
+      <x:c r="H14" s="10" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A15" s="10" t="str">
+        <x:v>SRC-024</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>budgetme savings closure profile and form responses</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str">
+        <x:v>knowledge/corpus/budgetme_requirements_021_025.md</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="str">
+        <x:v>Source-derived SRS extract</x:v>
+      </x:c>
+      <x:c r="E15" s="10" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; SRS=C:/Users/HP/Desktop/capstone/BudgetMe_Software_Requirements_Specification.docx; SRS_version=1.0; SRS_sha256=d90dd05f4a43bb17699eb6787672cc55571e65617c462fdcf08a26688eddad22</x:v>
+      </x:c>
+      <x:c r="F15" s="10" t="str">
+        <x:v>Source-derived requirements; PT targets distinguished</x:v>
+      </x:c>
+      <x:c r="G15" s="10" t="str">
+        <x:v>Preserves FR-021 to FR-025, their acceptance criteria, related quality targets and unresolved decisions.</x:v>
+      </x:c>
+      <x:c r="H15" s="10" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A16" s="10" t="str">
+        <x:v>SRC-025</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>budgetme summary realtime and browser behavior</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str">
+        <x:v>knowledge/corpus/budgetme_requirements_026_030.md</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="str">
+        <x:v>Source-derived SRS extract</x:v>
+      </x:c>
+      <x:c r="E16" s="10" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; SRS=C:/Users/HP/Desktop/capstone/BudgetMe_Software_Requirements_Specification.docx; SRS_version=1.0; SRS_sha256=d90dd05f4a43bb17699eb6787672cc55571e65617c462fdcf08a26688eddad22</x:v>
+      </x:c>
+      <x:c r="F16" s="10" t="str">
+        <x:v>Source-derived requirements; PT targets distinguished</x:v>
+      </x:c>
+      <x:c r="G16" s="10" t="str">
+        <x:v>Preserves FR-026 to FR-030, their acceptance criteria, related quality targets and unresolved decisions.</x:v>
+      </x:c>
+      <x:c r="H16" s="10" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A17" s="10" t="str">
+        <x:v>SRC-026</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>BudgetMe data rules and calculation boundaries</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str">
+        <x:v>knowledge/corpus/budgetme_data_rules.md</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="str">
+        <x:v>Source-derived repository document</x:v>
+      </x:c>
+      <x:c r="E17" s="10" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22</x:v>
+      </x:c>
+      <x:c r="F17" s="10" t="str">
+        <x:v>Primary source code; derived rules</x:v>
+      </x:c>
+      <x:c r="G17" s="10" t="str">
+        <x:v>Explains planning and balance formulas, public-form boundaries, relationships, closure and unresolved concurrency questions.</x:v>
+      </x:c>
+      <x:c r="H17" s="10" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A18" s="10" t="str">
+        <x:v>SRC-027</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>BudgetMe authentication and API contracts</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str">
+        <x:v>knowledge/corpus/budgetme_auth_api_contracts.md</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="str">
+        <x:v>Source-derived repository document</x:v>
+      </x:c>
+      <x:c r="E18" s="10" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22</x:v>
+      </x:c>
+      <x:c r="F18" s="10" t="str">
+        <x:v>Primary source code; derived contracts</x:v>
+      </x:c>
+      <x:c r="G18" s="10" t="str">
+        <x:v>Defines owner-specific authentication, history fragments, summary fields, Realtime JWT and form responses without inventing provider APIs.</x:v>
+      </x:c>
+      <x:c r="H18" s="10" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="66" hidden="0" customHeight="1">
+      <x:c r="A19" s="10" t="str">
+        <x:v>SRC-028</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>BudgetMe test coverage and execution evidence</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str">
+        <x:v>knowledge/corpus/budgetme_test_coverage.md</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="str">
+        <x:v>Repository and execution evidence summary</x:v>
+      </x:c>
+      <x:c r="E19" s="10" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; execution=evidence/traces/budgetme_tests_20261022T173303Z/verification.json; execution_sha256=cfd0e1fcde8f66603d32a1e82472e81bccddc8e037dc0854eb98b7129ad7a2d0</x:v>
+      </x:c>
+      <x:c r="F19" s="10" t="str">
+        <x:v>Primary test source and retained isolated run</x:v>
+      </x:c>
+      <x:c r="G19" s="10" t="str">
+        <x:v>Separates 51 existing definitions, 53 executed checks, two separate boundary assertions and unverified FR/AC coverage.</x:v>
+      </x:c>
+      <x:c r="H19" s="10" t="str">
+        <x:v>Authorized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="66" hidden="0" customHeight="1">
+      <x:c r="A20" s="10" t="str">
+        <x:v>SRC-029</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>BudgetMe observed test failures</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str">
+        <x:v>knowledge/corpus/budgetme_observed_failures.md</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="str">
+        <x:v>Repository and execution evidence summary</x:v>
+      </x:c>
+      <x:c r="E20" s="10" t="str">
+        <x:v>https://github.com/Joritace/BudgetMe; commit=a55e0b28ba5ce00c0ca6034854abbab9ae444938; retrieved=2026-10-22; execution=evidence/traces/budgetme_tests_20261022T173303Z/verification.json; execution_sha256=cfd0e1fcde8f66603d32a1e82472e81bccddc8e037dc0854eb98b7129ad7a2d0</x:v>
+      </x:c>
+      <x:c r="F20" s="10" t="str">
+        <x:v>Primary test source and retained isolated run</x:v>
+      </x:c>
+      <x:c r="G20" s="10" t="str">
+        <x:v>Explains the four retained target assertion failures and the separately resolved sandbox template-path discrepancy.</x:v>
+      </x:c>
+      <x:c r="H20" s="10" t="str">
         <x:v>Authorized</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R413c40bae23f4db7"/>
+  </x:tableParts>
 </x:worksheet>
 </file>